--- a/financial_advisor_forms/003_personal_budget_tracking_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/003_personal_budget_tracking_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,17 +520,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>personal_budet_form_page1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Personal Budget Tracking Form</t>
+          <t>What is your monthly income?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Please fill out this form to track your personal budget.</t>
+          <t>Enter your monthly income.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,17 +547,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>monthly_income_1</t>
+          <t>personal_budet_form_page2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monthly Income</t>
+          <t>Monthly Expenses</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enter your monthly income.</t>
+          <t>Enter your monthly expenses.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -569,22 +569,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>monthly_expenses_1</t>
+          <t>personal_budet_form_page3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monthly Expenses</t>
+          <t>Where does your income come from?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enter your monthly expenses.</t>
+          <t>Select your income source.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -596,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>progress_1</t>
+          <t>personal_budet_form_page4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How much are your monthly expenses?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select your expense level.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -624,12 +628,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_goals_1</t>
+          <t>personal_budet_form_page5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Goals</t>
+          <t>What are your financial goals?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -646,22 +650,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>income_source_1</t>
+          <t>personal_budet_form_page6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Income Source</t>
+          <t>How much progress you have made towards your financial goals?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enter your income source.</t>
+          <t>Select your progress level.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -678,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>monthly_expenses_2</t>
+          <t>personal_budet_form_page7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are your expenses for Rent?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select your rent expenses.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -696,22 +704,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>monthly_income_2</t>
+          <t>personal_budet_form_page8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monthly Income</t>
+          <t>What are your expenses for Food?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Enter your monthly income.</t>
+          <t>Select your food expenses.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -723,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>progress_2</t>
+          <t>personal_budet_form_page9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What are your expenses for Transportation?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select your transportation expenses.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -746,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>monthly_expenses_3</t>
+          <t>personal_budet_form_page10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What are your expenses for Healthcare?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select your healthcare expenses.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -769,22 +785,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monthly_income_3</t>
+          <t>personal_budet_form_page11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monthly Income</t>
+          <t>What are your expenses for Entertainment?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enter your monthly income.</t>
+          <t>Select your entertainment expenses.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -796,356 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monthly_expenses_4</t>
+          <t>personal_budet_form_page12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monthly Expenses</t>
+          <t>What are your total expenses for Miscellaneous?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enter your monthly expenses.</t>
+          <t>Select your miscellaneous expenses.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>monthly_income_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>monthly_expenses_5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Enter your monthly expenses.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>monthly_income_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter your monthly income.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>monthly_expenses_6</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>monthly_income_6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter your monthly income.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>monthly_expenses_7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter your monthly expenses.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>monthly_income_7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter your monthly income.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>monthly_expenses_8</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>monthly_income_8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>monthly_expenses_9</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter your monthly expenses.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>monthly_income_9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>monthly_expenses_10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Monthly Expenses</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter your monthly expenses.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>monthly_income_10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Monthly Income</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Enter your monthly income.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1162,10 +847,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1190,304 +875,474 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>healthcare</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>monthly_expenses_2_choices</t>
+          <t>personal_budet_form_page4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>miscellaneous</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>progress_2_choices</t>
+          <t>personal_budet_form_page4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>on_track</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>progress_2_choices</t>
+          <t>personal_budet_form_page6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>behind_schedule</t>
+          <t>on_track</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behind Schedule</t>
+          <t>On Track</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>progress_2_choices</t>
+          <t>personal_budet_form_page6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ahead_of_schedule</t>
+          <t>behind_schedule</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ahead of Schedule</t>
+          <t>Behind Schedule</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rent</t>
+          <t>ahead_of_schedule</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Ahead of Schedule</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>healthcare</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>monthly_expenses_6_choices</t>
+          <t>personal_budet_form_page8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>miscellaneous</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>monthly_expenses_8_choices</t>
+          <t>personal_budet_form_page8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>monthly_expenses_8_choices</t>
+          <t>personal_budet_form_page9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>monthly_expenses_8_choices</t>
+          <t>personal_budet_form_page9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page9_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page10_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page10_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page10_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page11_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page11_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page11_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page12_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page12_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>personal_budet_form_page12_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
